--- a/www/download/COUNTRY.MLT.WIOD16.xlsx
+++ b/www/download/COUNTRY.MLT.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01849541503962</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04258475303906</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00626333280302</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.876784928651374</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.809159412818347</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.803917831321913</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.795095670141333</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.727531039201796</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.681390847602003</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.717578476429816</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.751056851120209</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.719018035214085</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.779428556557194</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.753814975897154</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.753623085787195</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.153</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.168</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.168</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.176</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.177</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.179</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.183</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.194</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.135</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.139</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.147</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.142</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.161</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.172</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>320.074</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>306.075</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>317.4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>317.916</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>300.648</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>318.199</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>316.823</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>327.82</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>349.132</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>346.397</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>350.083</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>343.938</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>348.914</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>350.831</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>360.464</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>279.487</t>
+          <t>344374812.683157</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>268.753</t>
+          <t>312968728.72803</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>277.871</t>
+          <t>297214837.27335</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>277.043</t>
+          <t>324448280.175637</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>262.675</t>
+          <t>302712852.564131</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>277.219</t>
+          <t>302435220.935199</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>275.867</t>
+          <t>307825438.164213</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>285.294</t>
+          <t>325647809.009202</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>304.514</t>
+          <t>387811949.529857</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>292.19</t>
+          <t>350580046.52176</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>297.223</t>
+          <t>362969484.800659</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>300.784</t>
+          <t>329590094.532172</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>302.355</t>
+          <t>344377828.345991</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>305.79</t>
+          <t>333607833.134414</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>317.023</t>
+          <t>304662878.143173</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>106598549.463612</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>110253976.81798</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>115936708.53716</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>136525982.597501</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>128630446.276401</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>142318857.710135</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>138176105.393315</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>134807248.697673</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>153417062.937035</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>140290382.139663</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>131308703.210382</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>133962565.323281</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>137311918.724648</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>138998921.292378</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>136733175.270774</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2517090.48979362</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2469195.20477459</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2211245.90649712</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2315321.94178092</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1734024.42520912</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1692156.13387473</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1615243.26390987</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1472188.15771435</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1560080.72294286</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1465227.60659784</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1471874.95143449</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1367022.67123768</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1713414.61460579</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1395955.14346766</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1309247.02009047</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1261.36966843059</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1161.94659100099</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1199.42176636655</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1288.71606525316</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1320.37405501025</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1494.67442763686</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1502.48306301345</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1753.33712943439</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2031.29926669505</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1900.29092468059</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2110.66199415365</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2077.28651774519</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1967.06313047167</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1985.09793796169</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1950.27954270454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2798.17145122976</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2519.08332709182</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2406.63883179843</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2859.12574137855</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2949.22980168095</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3163.61789530174</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3401.72225538562</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4063.13870575219</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5251.99779137294</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4320.64489205989</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4955.92788839706</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4779.03101474672</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4865.3702501026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4708.52706842002</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4319.91833130665</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.62186494475148</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.43758100847182</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.39674735902078</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.029232785797</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.04209040397453</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.94787257613197</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.996488460973414</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.11631053045091</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.984877002403429</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.0827514726499</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.26354379209573</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.24528396626432</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.20195743245211</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.19994513019841</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.31855216828101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1106.13775198616</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1148.31969136966</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1192.10278820991</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1432.86045473778</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1637.21722068071</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1733.75001641791</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2000.6854906638</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2394.36326444445</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2841.45162892964</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2833.63266979318</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2834.22701336085</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3064.77138852171</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3064.97198752232</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>3227.48461346777</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>3442.68474147421</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01849541503962</t>
+          <t>802.881294446123</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04258475303906</t>
+          <t>828.914944876173</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00626333280302</t>
+          <t>862.752705292156</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.876784928651374</t>
+          <t>1017.33221011551</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.809159412818347</t>
+          <t>968.675700552762</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803917831321913</t>
+          <t>1051.87625802021</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.795095670141333</t>
+          <t>1023.67836267088</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.727531039201796</t>
+          <t>969.417867810104</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.681390847602003</t>
+          <t>1041.24516721213</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717578476429816</t>
+          <t>986.016180346238</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.751056851120209</t>
+          <t>873.876635234804</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.719018035214085</t>
+          <t>857.964425024217</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.779428556557194</t>
+          <t>878.065729151096</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.753814975897154</t>
+          <t>864.421152315785</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.753623085787195</t>
+          <t>796.674097015522</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-57374224.8962776</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-31602116.0545619</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-9228687.11910079</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>16636131.2857438</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6400080.19372415</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>21271907.8080217</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>40248065.6424836</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>79960695.3739887</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>119434752.534517</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>95326125.7423651</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>101801217.367778</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>119436399.364885</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>145965044.373815</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>163885148.352612</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>170156478.720515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>8011693.6301631</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>17656085.5154516</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>31505325.6211604</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>62860867.750037</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>47730490.6083402</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>29455111.2582979</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3871247.57569967</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-8049148.07576278</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-8220379.66361231</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-51879626.0909075</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-46399459.9467728</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-68919449.6747101</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-48045766.3663591</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-59276747.4671964</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-70304103.2532639</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-65385918.5264407</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-49258201.5700136</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-40734012.7402612</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-46224736.4642932</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>-41330410.4146161</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-8183203.45027616</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>36376818.066784</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>88009843.4497515</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>127655132.198129</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>147205751.833273</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>148200677.31455</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>188355849.039595</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>194010810.740174</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>223161895.819809</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>240460581.973779</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2105.04632070498</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2020.54732726863</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2067.80026789701</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2064.40387481371</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1978.1233526621</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2048.92091648189</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2043.76203882057</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2051.58924205379</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>2066.74358626307</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>2053.62665167276</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1978.05803274325</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1926.37376713206</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1933.46335848574</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1901.67910447761</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1847.13045504865</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2119.69441836113</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2031.42621661414</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2081.85815027984</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2080.19090606572</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1990.51956617716</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2063.41651932299</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2059.02725101377</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2066.05167907417</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2082.62989003361</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2064.3432561812</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1988.08940648279</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1941.17669785137</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1950.98223135563</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1920.04533737114</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1861.90088147969</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3097.21935713824</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2852.29108387519</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3360.24903155674</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4125.59732624925</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4448.375147617</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4937.66913152538</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6429.69733700578</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>8372.95796506221</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>11446.1082884171</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>10785.2021282688</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>11303.3030190379</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>12793.7014769513</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12687.5767547319</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>13279.3212526619</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>13420.3691467695</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>102307896.844973</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>92682386.1973608</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>97793252.0800467</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>110613567.805012</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>101356946.624991</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>93990299.7427455</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>100552884.360818</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>107211529.322866</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>127784034.877335</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>97590516.9470044</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>111474930.218186</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>99966913.251593</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>107731497.308718</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>100691067.805107</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>84838568.3603997</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>4541.94250077642</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4015.65770334658</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4316.5244145265</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5220.78900422165</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5661.18115133599</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6164.76088514223</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>7702.12538052424</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>9306.07961898767</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>12304.8706207096</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>11809.36228621</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>12334.668111906</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>13556.867194741</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13298.7487357501</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>13646.9125036835</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>13584.0819431903</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>320.074</t>
+          <t>268144767.802218</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>306.075</t>
+          <t>247323503.224956</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>242979672.496587</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>317.916</t>
+          <t>293879371.961259</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>300.648</t>
+          <t>275118174.684767</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>318.199</t>
+          <t>269988745.435141</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>316.823</t>
+          <t>286833640.589146</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>327.82</t>
+          <t>278432176.678699</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>349.132</t>
+          <t>321150911.055972</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>346.397</t>
+          <t>292618470.669978</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>350.083</t>
+          <t>302471467.119084</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>343.938</t>
+          <t>282020543.498489</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>348.914</t>
+          <t>304380454.145906</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>350.831</t>
+          <t>295229688.611638</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>360.464</t>
+          <t>268513805.91208</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>279.487</t>
+          <t>-1444.72314363818</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>268.753</t>
+          <t>-1163.36661947138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>277.871</t>
+          <t>-956.275382969758</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>277.043</t>
+          <t>-1095.19167797241</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>262.675</t>
+          <t>-1212.80600371899</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>277.219</t>
+          <t>-1227.09175361685</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>275.867</t>
+          <t>-1272.42804351845</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>285.294</t>
+          <t>-933.121653925456</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>304.514</t>
+          <t>-858.762332292501</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>292.19</t>
+          <t>-1024.16015794124</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>297.223</t>
+          <t>-1031.36509286812</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>300.784</t>
+          <t>-763.165717789779</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>302.355</t>
+          <t>-611.171981018201</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>305.79</t>
+          <t>-367.591251021612</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>317.023</t>
+          <t>-163.712796420809</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>344.393</t>
+          <t>-165836870.957245</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>313.032</t>
+          <t>-154641117.027595</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>297.283</t>
+          <t>-145186420.41654</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>324.475</t>
+          <t>-183265804.156247</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>302.741</t>
+          <t>-173761228.059776</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>302.461</t>
+          <t>-175998445.692396</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>307.826</t>
+          <t>-186280756.228328</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>325.752</t>
+          <t>-171220647.355834</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>387.901</t>
+          <t>-193366876.178637</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>350.609</t>
+          <t>-195027953.722974</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>363.03</t>
+          <t>-190996536.900898</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>329.691</t>
+          <t>-182053630.246896</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>344.425</t>
+          <t>-196648956.837188</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>333.612</t>
+          <t>-194538620.806531</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>304.638</t>
+          <t>-183675237.55168</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1603.77366369294</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1524.56237244476</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1712.32757394508</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2084.28345945465</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2178.7529563937</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2185.09337997861</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2249.3149712906</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2517.36428992946</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2931.12981777364</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2895.40667813482</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2960.9625691469</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2857.00309507039</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2623.24700341712</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2987.08127220377</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3012.95555060853</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>155.239</t>
+          <t>0.0500029134955713</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>144.359</t>
+          <t>0.0386923335937276</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>148.126</t>
+          <t>0.046798719585353</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>146.241</t>
+          <t>0.0472366477777477</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>135.525</t>
+          <t>0.0386123815515555</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>142.888</t>
+          <t>0.0230004707729087</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>135.961</t>
+          <t>0.0146934788409264</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>140.524</t>
+          <t>0.0146919198879723</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>149.993</t>
+          <t>-0.00448598742472988</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>154.191</t>
+          <t>0.00982796203882271</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>154.584</t>
+          <t>0.0168308564290895</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>143.262</t>
+          <t>0.0118141902001873</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>139.232</t>
+          <t>0.0123780443441908</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>140.648</t>
+          <t>0.0209755184373619</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>137.544</t>
+          <t>0.0163431103819854</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1785.54433566473</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1838.860702122</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2001.81793467317</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2436.47395366833</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2728.20225805487</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3073.21030878091</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3225.04177361075</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3731.43713926947</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4671.46050985369</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3790.56083303838</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3822.0849264098</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4430.37902021936</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4213.1947512616</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4575.46742803734</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4980.91920075766</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>106.605</t>
+          <t>2006.90042983854</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>110.268</t>
+          <t>2051.16313074228</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>115.958</t>
+          <t>2235.11320414116</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>136.538</t>
+          <t>2730.39966196382</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>128.633</t>
+          <t>3061.05654089106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>142.325</t>
+          <t>3461.54580393645</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>138.181</t>
+          <t>3628.74126338817</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>134.832</t>
+          <t>4187.65925957624</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>153.437</t>
+          <t>5236.77792014259</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>140.303</t>
+          <t>4355.41272667832</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>131.327</t>
+          <t>4368.69562097534</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>133.993</t>
+          <t>4963.58131937692</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>137.328</t>
+          <t>4745.59666240938</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>138.998</t>
+          <t>5122.78567635186</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>136.723</t>
+          <t>5519.3494688472</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>162.17</t>
+          <t>10579.1306865473</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>143.73</t>
+          <t>11021.5764852424</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>139.63</t>
+          <t>12039.2294788405</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>14331.8630927035</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>104.21</t>
+          <t>16233.6780725241</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>94.78</t>
+          <t>16734.0385936516</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>99.64</t>
+          <t>18769.599064396</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>111.59</t>
+          <t>22307.3358096678</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>98.46</t>
+          <t>26567.3245566894</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>108.26</t>
+          <t>26538.6946478904</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>126.32</t>
+          <t>26020.5938311373</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>124.48</t>
+          <t>28456.5293535819</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>120.17</t>
+          <t>27623.132965109</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>29183.7326324026</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>131.87</t>
+          <t>30325.7216933288</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.517</t>
+          <t>2874.72015174622</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2882.70230473486</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>2885.35001226786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>2958.38745678843</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>2920.75831487519</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>3195.12837903294</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>3196.09862693439</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>3274.96139670962</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3625.80929152263</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>3044.87670064219</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>3233.5797615821</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>3509.51045558008</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>3647.59525687938</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>3859.53388864381</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>4163.03853590684</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2591.55304094242</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2611.12367760839</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2602.96304802785</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2660.09654667168</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2616.88924620119</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2845.0740128735</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2847.37261331815</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2928.97703288711</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3243.39178902387</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2657.22784281006</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2827.44165813488</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>3131.48193533076</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3235.14090473337</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>3446.13242197233</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>3752.53932858007</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1635.12510856392</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1574.77020546544</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1755.52331261388</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2109.84962364671</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2264.03819240213</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2118.64078200392</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2276.47619736918</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2722.10085507419</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2722.27094505961</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3094.45395335255</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>3272.17589233237</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3400.96223874214</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>3406.89235228992</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3839.62853536977</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>3938.30135852165</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>279487000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>268753000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>277871000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>277043000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>262675000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>277219000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>275867000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>285294000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>304514000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>292190000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>297223000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>300784000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>302355000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>305790000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>317023000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>320073857.17253</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>306074988.057252</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>317400093.591664</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>317915576.174024</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>300648075.275399</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>318199461.444798</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>316822523.113489</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>327820419.918699</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>349132074.765234</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>346396798.387206</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>350082663.587555</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>343937687.325305</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>348913662.255641</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>350830684.044455</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>360464010.654467</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>155238501.593279</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>144359237.157618</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>148126067.111763</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>146241106.137746</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>135524941.602045</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>142887733.509116</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>135961278.577105</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>140524465.445019</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>149992852.241784</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>154190889.883983</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>154583745.740108</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>143261899.251418</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>139231526.94844</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>140647852.719091</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>137543752.704324</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>151000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150670</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>152460</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>152830</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>151040</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>154210</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>153870</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>158670</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>167640</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>167800</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>176090</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>177180</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>178840</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>182720</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>193600</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>132770</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>133010</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134380</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>132790</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>135300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>134980</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>139060</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>147340</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>142280</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>150260</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>156140</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>156380</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>160800</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>171630</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>320073857.17253</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>306074988.057252</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>317400093.591664</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>317915576.174024</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>300648075.275399</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>318199461.444798</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>316822523.113489</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>327820419.918699</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>349132074.765234</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>346396798.387206</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>350082663.587555</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>343937687.325305</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>348913662.255641</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>350830684.044455</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>360464010.654467</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>279487000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>268753000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>277871000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>277043000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>262675000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>277219000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>275867000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>285294000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>304514000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>292190000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>297223000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>300784000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>302355000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>305790000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>317023000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>9348.10856948186</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8894.77516214479</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>9645.32939037522</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>11758.9497402579</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>13115.1277074974</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>14064.4587028943</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>16049.6943819924</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>19192.3312062274</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>23955.175567226</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>22662.8580002929</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>23315.1209811747</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>26274.5104106667</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>25867.0448644158</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>27688.114110653</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>28914.9279802297</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3642.10776948187</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3626.31860214479</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3990.73595037522</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4839.96494025787</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5324.83078749739</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5580.06993289429</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5904.94862199242</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6910.04725622738</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7958.901847226</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7449.72516741671</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>7641.00636035809</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8364.58547363882</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>8152.80826089692</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>8962.40789846854</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>9457.72887404843</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>14934.7112020177</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15394.4875225605</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>15562.444666964</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>15553.4430301696</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>15462.0665047953</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>15366.9124537457</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>16422.6412286471</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>17176.4956690413</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>18226.6481470626</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>18705.3812318598</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>19185.793424339</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>19954.2884086967</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>21131.6036248189</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>22270.7851077483</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>23857.8905068317</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
